--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484660_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484660_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.094</v>
+        <v>3.6194</v>
       </c>
       <c r="E2" t="n">
-        <v>4.854</v>
+        <v>5.1564</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.76</v>
+        <v>-1.537</v>
       </c>
       <c r="G2" t="n">
         <v>3.682</v>
@@ -610,13 +610,13 @@
         <v>0.5498</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4224</v>
+        <v>0.9478</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4012</v>
+        <v>0.7036</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0212</v>
+        <v>0.2441</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6439</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>A. ALBA GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.747</v>
+        <v>1.6827</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5178</v>
+        <v>0.6332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2292</v>
+        <v>1.0495</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.9962</v>
+        <v>1.191</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3515</v>
+        <v>0.3865</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6447</v>
+        <v>0.8045</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4053</v>
+        <v>0.8477</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6713</v>
+        <v>0.1392</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.266</v>
+        <v>0.7085</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4015</v>
+        <v>0.3433</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0228</v>
+        <v>0.2472</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3787</v>
+        <v>0.0961</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.5656</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="S3" t="n">
-        <v>6.6753</v>
+        <v>0.2247</v>
       </c>
       <c r="T3" t="n">
-        <v>5.1441</v>
+        <v>0.0683</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5312</v>
+        <v>0.1565</v>
       </c>
       <c r="V3" t="n">
         <v>0.6335</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.652</v>
+        <v>1.6709</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5936</v>
+        <v>1.786</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0584</v>
+        <v>-0.1151</v>
       </c>
       <c r="G4" t="n">
         <v>1.539</v>
@@ -766,13 +766,13 @@
         <v>0.5498</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1149</v>
+        <v>-0.096</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1053</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3219</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALBA GONZALEZ</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3447</v>
+        <v>1.1711</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3447</v>
+        <v>0.4249</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.7462</v>
       </c>
       <c r="G5" t="n">
-        <v>1.191</v>
+        <v>1.7389</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3865</v>
+        <v>-0.4699</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8045</v>
+        <v>2.2087</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8477</v>
+        <v>3.084</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1392</v>
+        <v>0.907</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7085</v>
+        <v>2.1769</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3433</v>
+        <v>-1.3451</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2472</v>
+        <v>-1.3769</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0961</v>
+        <v>0.0318</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3665</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1133</v>
+        <v>0.77</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2202</v>
+        <v>0.0898</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1069</v>
+        <v>0.6802</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6335</v>
+        <v>0.3115</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2121</v>
+        <v>0.9679</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7054</v>
+        <v>1.486</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4933</v>
+        <v>-0.5181</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3852</v>
@@ -922,13 +922,13 @@
         <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7414</v>
+        <v>1.4972</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0777</v>
+        <v>0.8583</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6637</v>
+        <v>0.6389</v>
       </c>
       <c r="V6" t="n">
         <v>0.9554</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>D. ARIJA DE LA PEÑA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.6251</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0699</v>
+        <v>0.6251</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9444</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7389</v>
+        <v>0.6251</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4699</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2087</v>
+        <v>0.6251</v>
       </c>
       <c r="J7" t="n">
-        <v>3.084</v>
+        <v>0.6251</v>
       </c>
       <c r="K7" t="n">
-        <v>0.907</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1769</v>
+        <v>0.6251</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3451</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3769</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0318</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4734</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.405</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8784</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PEÑA</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6251</v>
+        <v>0.2543</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6251</v>
+        <v>1.689</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-1.4347</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6251</v>
+        <v>-0.5454</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.1054</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6251</v>
+        <v>-1.6508</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6251</v>
+        <v>2.3874</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.3004</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6251</v>
+        <v>-0.9131</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-2.9327</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-2.195</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.7377</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.6714</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.8123</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.8591</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0888</v>
+        <v>-0.0393</v>
       </c>
       <c r="E9" t="n">
         <v>-0.6228</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5339</v>
+        <v>0.5835</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3051</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1502</v>
+        <v>-0.1007</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0401</v>
+        <v>0.0094</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>M. PERAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8917</v>
+        <v>-0.4623</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6173</v>
+        <v>0.9921</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.509</v>
+        <v>-1.4544</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5454</v>
+        <v>0.1243</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1054</v>
+        <v>-0.2094</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6508</v>
+        <v>0.3337</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3874</v>
+        <v>1.4359</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3004</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9131</v>
+        <v>0.8789</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9327</v>
+        <v>-1.3116</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.195</v>
+        <v>-0.7664</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7377</v>
+        <v>-0.5452</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5498</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5254</v>
+        <v>0.6412</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2594</v>
+        <v>0.4333</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.2079</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3219</v>
+        <v>-0.3115</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>0.9554</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6439</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PERAL</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6666</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2089</v>
+        <v>-0.394</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8755</v>
+        <v>-0.1176</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1243</v>
+        <v>-1.9962</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2094</v>
+        <v>-0.3515</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3337</v>
+        <v>-1.6447</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4359</v>
+        <v>0.4053</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.6713</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8789</v>
+        <v>-0.266</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3116</v>
+        <v>-2.4015</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7664</v>
+        <v>-1.0228</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5452</v>
+        <v>-1.3787</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9163</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5631</v>
+        <v>3.4167</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3499</v>
+        <v>2.2323</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2132</v>
+        <v>1.1844</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3115</v>
+        <v>0.6335</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9554</v>
+        <v>0.6335</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3127</v>
+        <v>-2.4118</v>
       </c>
       <c r="E12" t="n">
         <v>-0.9497</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3631</v>
+        <v>-1.4621</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2836</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1541</v>
+        <v>0.0551</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2092</v>
+        <v>0.1101</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0155</v>
+        <v>-4.1665</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2523</v>
+        <v>-2.428</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7632</v>
+        <v>-1.7385</v>
       </c>
       <c r="G13" t="n">
         <v>-2.262</v>
@@ -1468,13 +1468,13 @@
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4743</v>
+        <v>1.3233</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0746</v>
+        <v>0.7496</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5737</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5785</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.574099999999997</v>
+        <v>2.3999</v>
       </c>
       <c r="E14" t="n">
-        <v>7.572100000000001</v>
+        <v>8.398200000000003</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.9982</v>
+        <v>-5.9983</v>
       </c>
       <c r="G14" t="n">
         <v>3.1228</v>
@@ -1516,7 +1516,7 @@
         <v>-4.0905</v>
       </c>
       <c r="I14" t="n">
-        <v>7.2133</v>
+        <v>7.213299999999998</v>
       </c>
       <c r="J14" t="n">
         <v>15.9096</v>
@@ -1531,7 +1531,7 @@
         <v>-12.7865</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.738999999999999</v>
+        <v>-9.739000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-3.0474</v>
@@ -1546,19 +1546,19 @@
         <v>8.246499999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>9.524799999999997</v>
+        <v>10.3507</v>
       </c>
       <c r="T14" t="n">
-        <v>4.928499999999999</v>
+        <v>5.7544</v>
       </c>
       <c r="U14" t="n">
-        <v>4.596299999999999</v>
+        <v>4.5962</v>
       </c>
       <c r="V14" t="n">
         <v>-1.9108</v>
       </c>
       <c r="W14" t="n">
-        <v>4.1436</v>
+        <v>4.143599999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-6.0546</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2866</v>
+        <v>3.8912</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8117</v>
+        <v>5.2925</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5251</v>
+        <v>-1.4013</v>
       </c>
       <c r="G15" t="n">
         <v>1.2677</v>
@@ -1624,13 +1624,13 @@
         <v>3.2986</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.4823</v>
+        <v>-1.8776</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2481</v>
+        <v>-0.7673</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2342</v>
+        <v>-1.1103</v>
       </c>
       <c r="V15" t="n">
         <v>1.2026</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1382</v>
+        <v>2.498</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8193</v>
+        <v>3.2039</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6811</v>
+        <v>-0.7059</v>
       </c>
       <c r="G16" t="n">
         <v>0.281</v>
@@ -1702,13 +1702,13 @@
         <v>2.0158</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6832</v>
+        <v>-1.3233</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1561</v>
+        <v>-0.7715</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5271</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>1.5245</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7169</v>
+        <v>0.7882</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4634</v>
+        <v>-0.3672</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1802</v>
+        <v>1.1554</v>
       </c>
       <c r="G17" t="n">
         <v>1.1447</v>
@@ -1780,13 +1780,13 @@
         <v>2.5656</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0128</v>
+        <v>-1.9414</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0829</v>
+        <v>-0.9868</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9298</v>
+        <v>-0.9546</v>
       </c>
       <c r="V17" t="n">
         <v>-0.0644</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>C. FAJARDO PANOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2694</v>
+        <v>-0.1021</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0351</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7656</v>
+        <v>-0.7901</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6065</v>
+        <v>-0.6885</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1759</v>
+        <v>-1.5315</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7824</v>
+        <v>0.843</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3383</v>
+        <v>0.7159</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2292</v>
+        <v>-0.576</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1091</v>
+        <v>1.2919</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9448</v>
+        <v>-1.4044</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0532</v>
+        <v>-0.9555</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8916</v>
+        <v>-0.4489</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3906</v>
+        <v>0.0366</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2074</v>
+        <v>-0.0279</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1832</v>
+        <v>0.0645</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6979</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0346</v>
+        <v>-0.4251</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0057</v>
+        <v>0.8134</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0403</v>
+        <v>-1.2385</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0683</v>
@@ -1936,13 +1936,13 @@
         <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3878</v>
+        <v>-0.7783</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3318</v>
+        <v>-0.5241</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.056</v>
+        <v>-0.2542</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3115</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. FAJARDO PANOS</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2449</v>
+        <v>-1.0112</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4957</v>
+        <v>0.9774</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7406</v>
+        <v>-1.9886</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6885</v>
+        <v>-0.6065</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5315</v>
+        <v>1.1759</v>
       </c>
       <c r="I20" t="n">
-        <v>0.843</v>
+        <v>-1.7824</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7159</v>
+        <v>2.3383</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.576</v>
+        <v>2.2292</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2919</v>
+        <v>0.1091</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4044</v>
+        <v>-2.9448</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9555</v>
+        <v>-1.0532</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4489</v>
+        <v>-1.8916</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5498</v>
+        <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1062</v>
+        <v>0.1099</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2202</v>
+        <v>0.1497</v>
       </c>
       <c r="U20" t="n">
-        <v>0.114</v>
+        <v>-0.0398</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6979</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0198</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5123</v>
+        <v>-1.0149</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4029</v>
+        <v>-0.174</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9152</v>
+        <v>-0.8409</v>
       </c>
       <c r="G21" t="n">
         <v>1.2625</v>
@@ -2092,13 +2092,13 @@
         <v>1.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8298</v>
+        <v>-1.3324</v>
       </c>
       <c r="T21" t="n">
-        <v>0.034</v>
+        <v>-0.543</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8638</v>
+        <v>-0.7894</v>
       </c>
       <c r="V21" t="n">
         <v>-0.945</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4097</v>
+        <v>-1.8239</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2994</v>
+        <v>-1.0109</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1103</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3549</v>
@@ -2170,13 +2170,13 @@
         <v>2.3823</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.8071</v>
+        <v>-2.2213</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2111</v>
+        <v>-0.9227</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5959</v>
+        <v>-1.2987</v>
       </c>
       <c r="V22" t="n">
         <v>1.2026</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7838</v>
+        <v>-4.3744</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8094</v>
+        <v>-3.4248</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.9495</v>
       </c>
       <c r="G23" t="n">
         <v>-4.3606</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.197</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5875</v>
+        <v>-0.2029</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0189</v>
+        <v>0.0058</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.574200000000001</v>
+        <v>-1.574199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>5.998200000000001</v>
+        <v>5.998300000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.5723</v>
+        <v>-7.5724</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1229</v>
@@ -2305,34 +2305,34 @@
         <v>9.739199999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>3.0473</v>
+        <v>3.047299999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-15.9095</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.648400000000001</v>
+        <v>-5.6484</v>
       </c>
       <c r="O24" t="n">
         <v>-10.2611</v>
       </c>
       <c r="P24" t="n">
-        <v>9.162899999999999</v>
+        <v>9.1629</v>
       </c>
       <c r="Q24" t="n">
-        <v>-8.246700000000001</v>
+        <v>-8.246699999999999</v>
       </c>
       <c r="R24" t="n">
         <v>17.4093</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.525</v>
+        <v>-9.524799999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.5963</v>
+        <v>-4.596499999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.928500000000001</v>
+        <v>-4.9286</v>
       </c>
       <c r="V24" t="n">
         <v>1.9109</v>
